--- a/docs/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/docs/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Decisions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$J$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$J$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$I$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$G$12</definedName>
   </definedNames>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="B5" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$284,A5)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$285,A5)</f>
         <v/>
       </c>
     </row>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B6" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$284,A6)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$285,A6)</f>
         <v/>
       </c>
     </row>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B7" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$284,A7)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$285,A7)</f>
         <v/>
       </c>
     </row>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B8" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$284,A8)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$285,A8)</f>
         <v/>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B9" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$284,A9)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$285,A9)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B10" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$284,A10)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$285,A10)</f>
         <v/>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="B11" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$284,A11)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$285,A11)</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B12" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$284,A12)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$285,A12)</f>
         <v/>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B16" s="19">
-        <f>COUNTIFS(Tasks!$A$2:$A$284,"HR-*",Tasks!$E$2:$E$284,"Done")+COUNTIFS(Tasks!$A$2:$A$284,"HR-*",Tasks!$E$2:$E$284,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$285,"HR-*",Tasks!$E$2:$E$285,"Done")+COUNTIFS(Tasks!$A$2:$A$285,"HR-*",Tasks!$E$2:$E$285,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C16" s="19">
@@ -1085,7 +1085,7 @@
         <v/>
       </c>
       <c r="D16" s="19">
-        <f>COUNTIF(Tasks!$A$2:$A$284,"HR-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$285,"HR-*")</f>
         <v/>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="B17" s="19">
-        <f>COUNTIFS(Tasks!$A$2:$A$284,"JM-*",Tasks!$E$2:$E$284,"Done")+COUNTIFS(Tasks!$A$2:$A$284,"JM-*",Tasks!$E$2:$E$284,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$285,"JM-*",Tasks!$E$2:$E$285,"Done")+COUNTIFS(Tasks!$A$2:$A$285,"JM-*",Tasks!$E$2:$E$285,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C17" s="19">
@@ -1104,7 +1104,7 @@
         <v/>
       </c>
       <c r="D17" s="19">
-        <f>COUNTIF(Tasks!$A$2:$A$284,"JM-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$285,"JM-*")</f>
         <v/>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B20" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$284,"Earlier (May – 5 Oct 2026)")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$285,"Earlier (May – 5 Oct 2026)")</f>
         <v/>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="B21" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$284,"19 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$285,"19 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B22" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$284,"20 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$285,"20 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="B23" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$284,"21 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$285,"21 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B24" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$284,"—")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$285,"—")</f>
         <v/>
       </c>
     </row>
@@ -1236,39 +1236,39 @@
         </is>
       </c>
       <c r="B27" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A27,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A27,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C27" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A27,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A27,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D27" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A27,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A27,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E27" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A27,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A27,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F27" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A27,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A27,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G27" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A27,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A27,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H27" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A27,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A27,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I27" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A27,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A27,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J27" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A27)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A27)</f>
         <v/>
       </c>
     </row>
@@ -1279,39 +1279,39 @@
         </is>
       </c>
       <c r="B28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A28,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A28,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A28,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A28,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A28,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A28,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A28,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A28,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A28,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A28,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A28,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A28,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A28,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A28,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A28,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A28,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J28" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A28)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A28)</f>
         <v/>
       </c>
     </row>
@@ -1322,39 +1322,39 @@
         </is>
       </c>
       <c r="B29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A29,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A29,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A29,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A29,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A29,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A29,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A29,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A29,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A29,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A29,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A29,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A29,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A29,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A29,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A29,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A29,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J29" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A29)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A29)</f>
         <v/>
       </c>
     </row>
@@ -1365,39 +1365,39 @@
         </is>
       </c>
       <c r="B30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A30,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A30,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A30,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A30,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A30,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A30,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A30,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A30,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A30,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A30,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A30,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A30,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A30,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A30,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A30,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A30,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J30" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A30)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A30)</f>
         <v/>
       </c>
     </row>
@@ -1408,39 +1408,39 @@
         </is>
       </c>
       <c r="B31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A31,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A31,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A31,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A31,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A31,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A31,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A31,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A31,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A31,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A31,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A31,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A31,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A31,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A31,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A31,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A31,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J31" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A31)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A31)</f>
         <v/>
       </c>
     </row>
@@ -1451,39 +1451,39 @@
         </is>
       </c>
       <c r="B32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A32,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A32,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A32,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A32,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A32,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A32,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A32,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A32,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A32,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A32,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A32,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A32,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A32,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A32,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A32,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A32,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J32" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A32)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A32)</f>
         <v/>
       </c>
     </row>
@@ -1494,39 +1494,39 @@
         </is>
       </c>
       <c r="B33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A33,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A33,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A33,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A33,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A33,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A33,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A33,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A33,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A33,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A33,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A33,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A33,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A33,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A33,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A33,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A33,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J33" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A33)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A33)</f>
         <v/>
       </c>
     </row>
@@ -1537,39 +1537,39 @@
         </is>
       </c>
       <c r="B34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A34,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A34,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A34,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A34,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A34,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A34,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A34,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A34,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A34,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A34,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A34,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A34,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A34,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A34,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A34,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A34,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J34" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A34)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A34)</f>
         <v/>
       </c>
     </row>
@@ -1580,39 +1580,39 @@
         </is>
       </c>
       <c r="B35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A35,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A35,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A35,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A35,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A35,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A35,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A35,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A35,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A35,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A35,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A35,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A35,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A35,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A35,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A35,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A35,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J35" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A35)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A35)</f>
         <v/>
       </c>
     </row>
@@ -1623,39 +1623,39 @@
         </is>
       </c>
       <c r="B36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A36,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A36,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A36,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A36,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A36,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A36,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A36,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A36,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A36,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A36,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A36,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A36,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A36,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A36,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A36,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A36,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J36" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A36)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A36)</f>
         <v/>
       </c>
     </row>
@@ -1666,39 +1666,39 @@
         </is>
       </c>
       <c r="B37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A37,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A37,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A37,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A37,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A37,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A37,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A37,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A37,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A37,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A37,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A37,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A37,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A37,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A37,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A37,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A37,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J37" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A37)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A37)</f>
         <v/>
       </c>
     </row>
@@ -1709,39 +1709,39 @@
         </is>
       </c>
       <c r="B38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A38,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A38,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A38,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A38,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A38,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A38,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A38,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A38,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A38,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A38,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A38,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A38,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A38,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A38,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A38,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A38,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J38" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A38)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A38)</f>
         <v/>
       </c>
     </row>
@@ -1752,39 +1752,39 @@
         </is>
       </c>
       <c r="B39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A39,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A39,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A39,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A39,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A39,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A39,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A39,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A39,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A39,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A39,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A39,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A39,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A39,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A39,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A39,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A39,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J39" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A39)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A39)</f>
         <v/>
       </c>
     </row>
@@ -1795,39 +1795,39 @@
         </is>
       </c>
       <c r="B40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A40,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A40,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A40,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A40,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A40,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A40,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A40,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A40,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A40,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A40,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A40,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A40,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A40,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A40,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A40,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A40,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J40" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A40)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A40)</f>
         <v/>
       </c>
     </row>
@@ -1838,39 +1838,39 @@
         </is>
       </c>
       <c r="B41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A41,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A41,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A41,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A41,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A41,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A41,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A41,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A41,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A41,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A41,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A41,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A41,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A41,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A41,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A41,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A41,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J41" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A41)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A41)</f>
         <v/>
       </c>
     </row>
@@ -1881,39 +1881,39 @@
         </is>
       </c>
       <c r="B42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A42,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A42,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A42,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A42,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A42,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A42,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A42,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A42,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A42,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A42,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A42,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A42,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A42,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A42,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A42,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A42,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J42" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A42)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A42)</f>
         <v/>
       </c>
     </row>
@@ -1924,39 +1924,39 @@
         </is>
       </c>
       <c r="B43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A43,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A43,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A43,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A43,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A43,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A43,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A43,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A43,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A43,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A43,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A43,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A43,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A43,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A43,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A43,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A43,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J43" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A43)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A43)</f>
         <v/>
       </c>
     </row>
@@ -1967,39 +1967,39 @@
         </is>
       </c>
       <c r="B44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A44,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A44,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A44,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A44,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A44,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A44,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A44,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A44,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A44,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A44,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A44,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A44,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A44,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A44,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A44,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A44,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J44" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A44)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A44)</f>
         <v/>
       </c>
     </row>
@@ -2010,39 +2010,39 @@
         </is>
       </c>
       <c r="B45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A45,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A45,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A45,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A45,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A45,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A45,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A45,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A45,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A45,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A45,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A45,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A45,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A45,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A45,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A45,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A45,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J45" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A45)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A45)</f>
         <v/>
       </c>
     </row>
@@ -2053,39 +2053,39 @@
         </is>
       </c>
       <c r="B46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A46,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A46,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A46,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A46,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A46,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A46,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A46,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A46,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A46,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A46,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A46,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A46,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A46,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A46,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A46,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A46,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J46" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A46)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A46)</f>
         <v/>
       </c>
     </row>
@@ -2096,39 +2096,39 @@
         </is>
       </c>
       <c r="B47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A47,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A47,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A47,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A47,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A47,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A47,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A47,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A47,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A47,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A47,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A47,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A47,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A47,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A47,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A47,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A47,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J47" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A47)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A47)</f>
         <v/>
       </c>
     </row>
@@ -2139,39 +2139,39 @@
         </is>
       </c>
       <c r="B48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A48,Tasks!$E$2:$E$284,B$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A48,Tasks!$E$2:$E$285,B$26)</f>
         <v/>
       </c>
       <c r="C48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A48,Tasks!$E$2:$E$284,C$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A48,Tasks!$E$2:$E$285,C$26)</f>
         <v/>
       </c>
       <c r="D48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A48,Tasks!$E$2:$E$284,D$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A48,Tasks!$E$2:$E$285,D$26)</f>
         <v/>
       </c>
       <c r="E48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A48,Tasks!$E$2:$E$284,E$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A48,Tasks!$E$2:$E$285,E$26)</f>
         <v/>
       </c>
       <c r="F48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A48,Tasks!$E$2:$E$284,F$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A48,Tasks!$E$2:$E$285,F$26)</f>
         <v/>
       </c>
       <c r="G48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A48,Tasks!$E$2:$E$284,G$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A48,Tasks!$E$2:$E$285,G$26)</f>
         <v/>
       </c>
       <c r="H48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A48,Tasks!$E$2:$E$284,H$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A48,Tasks!$E$2:$E$285,H$26)</f>
         <v/>
       </c>
       <c r="I48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$284,$A48,Tasks!$E$2:$E$284,I$26)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$285,$A48,Tasks!$E$2:$E$285,I$26)</f>
         <v/>
       </c>
       <c r="J48" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$284,$A48)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$285,$A48)</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4965,17 +4965,17 @@
     <row r="53">
       <c r="A53" s="29" t="inlineStr">
         <is>
-          <t>HR-62</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="B53" s="30" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>HR dashboard</t>
         </is>
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>HR User could not open the Holiday List ('Not permitted')</t>
+          <t>HR Portal and Employee Portal in the new college design</t>
         </is>
       </c>
       <c r="D53" s="30" t="inlineStr">
@@ -4995,39 +4995,39 @@
       </c>
       <c r="G53" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H53" s="31" t="inlineStr">
         <is>
-          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
+          <t>Same look as the Education team's new portals (Instructor Portal): left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so Education's changes cannot break these pages.</t>
         </is>
       </c>
       <c r="I53" s="31" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
         </is>
       </c>
       <c r="J53" s="31" t="inlineStr">
         <is>
-          <t>hr_core_permissions.py</t>
+          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="29" t="inlineStr">
         <is>
-          <t>HR-46</t>
+          <t>HR-62</t>
         </is>
       </c>
       <c r="B54" s="30" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C54" s="31" t="inlineStr">
         <is>
-          <t>Full end-to-end test with error sweep (round 3)</t>
+          <t>HR User could not open the Holiday List ('Not permitted')</t>
         </is>
       </c>
       <c r="D54" s="30" t="inlineStr">
@@ -5047,54 +5047,54 @@
       </c>
       <c r="G54" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H54" s="31" t="inlineStr">
         <is>
-          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
+          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
         </is>
       </c>
       <c r="I54" s="31" t="inlineStr">
         <is>
-          <t>Client UAT.</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="J54" s="31" t="inlineStr">
         <is>
-          <t>Test Report</t>
+          <t>hr_core_permissions.py</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="29" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-46</t>
         </is>
       </c>
       <c r="B55" s="30" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>System e-mail account password cannot be decrypted</t>
+          <t>Full end-to-end test with error sweep (round 3)</t>
         </is>
       </c>
       <c r="D55" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E55" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F55" s="30" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G55" s="30" t="inlineStr">
@@ -5104,34 +5104,34 @@
       </c>
       <c r="H55" s="31" t="inlineStr">
         <is>
-          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
+          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
         </is>
       </c>
       <c r="I55" s="31" t="inlineStr">
         <is>
-          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
+          <t>Client UAT.</t>
         </is>
       </c>
       <c r="J55" s="31" t="inlineStr">
         <is>
-          <t>Error Log; Email Queue</t>
+          <t>Test Report</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="29" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>HR-47</t>
         </is>
       </c>
       <c r="B56" s="30" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="C56" s="31" t="inlineStr">
         <is>
-          <t>Instructor form: linking an Employee fails on save</t>
+          <t>System e-mail account password cannot be decrypted</t>
         </is>
       </c>
       <c r="D56" s="30" t="inlineStr">
@@ -5141,49 +5141,49 @@
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Pending – other team</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Education team</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G56" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H56" s="31" t="inlineStr">
         <is>
-          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
+          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
         </is>
       </c>
       <c r="I56" s="31" t="inlineStr">
         <is>
-          <t>Education team: remove or map those fetches on Instructor.</t>
+          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
         </is>
       </c>
       <c r="J56" s="31" t="inlineStr">
         <is>
-          <t>education Instructor doctype</t>
+          <t>Error Log; Email Queue</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="29" t="inlineStr">
         <is>
-          <t>HR-49</t>
+          <t>HR-48</t>
         </is>
       </c>
       <c r="B57" s="30" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>Incomplete-employees report</t>
+          <t>Instructor form: linking an Employee fails on save</t>
         </is>
       </c>
       <c r="D57" s="30" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="E57" s="30" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Pending – other team</t>
         </is>
       </c>
       <c r="F57" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Education team</t>
         </is>
       </c>
       <c r="G57" s="30" t="inlineStr">
@@ -5208,24 +5208,24 @@
       </c>
       <c r="H57" s="31" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
         </is>
       </c>
       <c r="I57" s="31" t="inlineStr">
         <is>
-          <t>Report listing employees missing Ministry-mandatory fields.</t>
+          <t>Education team: remove or map those fetches on Instructor.</t>
         </is>
       </c>
       <c r="J57" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>education Instructor doctype</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
-          <t>HR-50</t>
+          <t>HR-49</t>
         </is>
       </c>
       <c r="B58" s="30" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="C58" s="31" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff</t>
+          <t>Incomplete-employees report</t>
         </is>
       </c>
       <c r="D58" s="30" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="H58" s="31" t="inlineStr">
         <is>
-          <t>Instructor sheet exists (HR-35).</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="I58" s="31" t="inlineStr">
         <is>
-          <t>Same export/import for non-academic staff.</t>
+          <t>Report listing employees missing Ministry-mandatory fields.</t>
         </is>
       </c>
       <c r="J58" s="31" t="inlineStr">
@@ -5277,17 +5277,17 @@
     <row r="59">
       <c r="A59" s="29" t="inlineStr">
         <is>
-          <t>HR-51</t>
+          <t>HR-50</t>
         </is>
       </c>
       <c r="B59" s="30" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>Duplicate fields on Employee Job Applicant</t>
+          <t>Data sheet for non-academic staff</t>
         </is>
       </c>
       <c r="D59" s="30" t="inlineStr">
@@ -5302,22 +5302,22 @@
       </c>
       <c r="F59" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem / Dinesh</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G59" s="30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H59" s="31" t="inlineStr">
         <is>
-          <t>Found during review.</t>
+          <t>Instructor sheet exists (HR-35).</t>
         </is>
       </c>
       <c r="I59" s="31" t="inlineStr">
         <is>
-          <t>Remove duplicated custom fields after checking data.</t>
+          <t>Same export/import for non-academic staff.</t>
         </is>
       </c>
       <c r="J59" s="31" t="inlineStr">
@@ -5329,17 +5329,17 @@
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
         <is>
-          <t>HR-52</t>
+          <t>HR-51</t>
         </is>
       </c>
       <c r="B60" s="30" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C60" s="31" t="inlineStr">
         <is>
-          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
+          <t>Duplicate fields on Employee Job Applicant</t>
         </is>
       </c>
       <c r="D60" s="30" t="inlineStr">
@@ -5349,49 +5349,49 @@
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – development</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem / Dinesh</t>
         </is>
       </c>
       <c r="G60" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H60" s="31" t="inlineStr">
         <is>
-          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
+          <t>Found during review.</t>
         </is>
       </c>
       <c r="I60" s="31" t="inlineStr">
         <is>
-          <t>Confirm whether 9-digit numbers must be accepted.</t>
+          <t>Remove duplicated custom fields after checking data.</t>
         </is>
       </c>
       <c r="J60" s="31" t="inlineStr">
         <is>
-          <t>ministry_lookup_validation.py</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="29" t="inlineStr">
         <is>
-          <t>HR-53</t>
+          <t>HR-52</t>
         </is>
       </c>
       <c r="B61" s="30" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
+          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
         </is>
       </c>
       <c r="D61" s="30" t="inlineStr">
@@ -5401,39 +5401,39 @@
       </c>
       <c r="E61" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F61" s="30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="G61" s="30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H61" s="31" t="inlineStr">
         <is>
-          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
+          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
         </is>
       </c>
       <c r="I61" s="31" t="inlineStr">
         <is>
-          <t>Complete or delete the demo record before go-live.</t>
+          <t>Confirm whether 9-digit numbers must be accepted.</t>
         </is>
       </c>
       <c r="J61" s="31" t="inlineStr">
         <is>
-          <t>Employee EMP-00001</t>
+          <t>ministry_lookup_validation.py</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="29" t="inlineStr">
         <is>
-          <t>HR-54</t>
+          <t>HR-53</t>
         </is>
       </c>
       <c r="B62" s="30" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="C62" s="31" t="inlineStr">
         <is>
-          <t>Website logo file missing (/files/rchs-logo.png)</t>
+          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
         </is>
       </c>
       <c r="D62" s="30" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G62" s="30" t="inlineStr">
@@ -5468,24 +5468,24 @@
       </c>
       <c r="H62" s="31" t="inlineStr">
         <is>
-          <t>Missing on the local copy; every page requests it.</t>
+          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
         </is>
       </c>
       <c r="I62" s="31" t="inlineStr">
         <is>
-          <t>Check the file exists on the live server.</t>
+          <t>Complete or delete the demo record before go-live.</t>
         </is>
       </c>
       <c r="J62" s="31" t="inlineStr">
         <is>
-          <t>Website Settings</t>
+          <t>Employee EMP-00001</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
-          <t>HR-55</t>
+          <t>HR-54</t>
         </is>
       </c>
       <c r="B63" s="30" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="C63" s="31" t="inlineStr">
         <is>
-          <t>Link the 216 existing Instructors to Employees</t>
+          <t>Website logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
       <c r="D63" s="30" t="inlineStr">
@@ -5510,44 +5510,44 @@
       </c>
       <c r="F63" s="30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G63" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H63" s="31" t="inlineStr">
         <is>
-          <t>Tool ready (HR-35). 1 of 216 linked.</t>
+          <t>Missing on the local copy; every page requests it.</t>
         </is>
       </c>
       <c r="I63" s="31" t="inlineStr">
         <is>
-          <t>HR fills the Instructor data sheet; run the import with commit.</t>
+          <t>Check the file exists on the live server.</t>
         </is>
       </c>
       <c r="J63" s="31" t="inlineStr">
         <is>
-          <t>instructor_data_sheet.py</t>
+          <t>Website Settings</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
         <is>
-          <t>HR-56</t>
+          <t>HR-55</t>
         </is>
       </c>
       <c r="B64" s="30" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C64" s="31" t="inlineStr">
         <is>
-          <t>Connect attendance devices</t>
+          <t>Link the 216 existing Instructors to Employees</t>
         </is>
       </c>
       <c r="D64" s="30" t="inlineStr">
@@ -5562,34 +5562,34 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G64" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H64" s="31" t="inlineStr">
         <is>
-          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
+          <t>Tool ready (HR-35). 1 of 216 linked.</t>
         </is>
       </c>
       <c r="I64" s="31" t="inlineStr">
         <is>
-          <t>Connect devices; map device user IDs to Employees.</t>
+          <t>HR fills the Instructor data sheet; run the import with commit.</t>
         </is>
       </c>
       <c r="J64" s="31" t="inlineStr">
         <is>
-          <t>bfac883</t>
+          <t>instructor_data_sheet.py</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
-          <t>HR-57</t>
+          <t>HR-56</t>
         </is>
       </c>
       <c r="B65" s="30" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="C65" s="31" t="inlineStr">
         <is>
-          <t>Set the Academic Holiday List</t>
+          <t>Connect attendance devices</t>
         </is>
       </c>
       <c r="D65" s="30" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="F65" s="30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="G65" s="30" t="inlineStr">
@@ -5624,34 +5624,34 @@
       </c>
       <c r="H65" s="31" t="inlineStr">
         <is>
-          <t>Not set; the page warns about it.</t>
+          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
         </is>
       </c>
       <c r="I65" s="31" t="inlineStr">
         <is>
-          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
+          <t>Connect devices; map device user IDs to Employees.</t>
         </is>
       </c>
       <c r="J65" s="31" t="inlineStr">
         <is>
-          <t>academic_presence_setup.py</t>
+          <t>bfac883</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="29" t="inlineStr">
         <is>
-          <t>HR-58</t>
+          <t>HR-57</t>
         </is>
       </c>
       <c r="B66" s="30" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C66" s="31" t="inlineStr">
         <is>
-          <t>Deploy to the live server</t>
+          <t>Set the Academic Holiday List</t>
         </is>
       </c>
       <c r="D66" s="30" t="inlineStr">
@@ -5666,59 +5666,59 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H66" s="31" t="inlineStr">
         <is>
-          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both).</t>
+          <t>Not set; the page warns about it.</t>
         </is>
       </c>
       <c r="I66" s="31" t="inlineStr">
         <is>
-          <t>Merge, pull on the server, bench migrate, restart; smoke-test with the Test Cases workbook.</t>
+          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
         </is>
       </c>
       <c r="J66" s="31" t="inlineStr">
         <is>
-          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
+          <t>academic_presence_setup.py</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="29" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>HR-58</t>
         </is>
       </c>
       <c r="B67" s="30" t="inlineStr">
         <is>
-          <t>Jameah</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C67" s="31" t="inlineStr">
         <is>
-          <t>Research: Jameah system, Ministry documents, view contract</t>
+          <t>Deploy to the live server</t>
         </is>
       </c>
       <c r="D67" s="30" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E67" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F67" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G67" s="30" t="inlineStr">
@@ -5728,24 +5728,24 @@
       </c>
       <c r="H67" s="31" t="inlineStr">
         <is>
-          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
+          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both).</t>
         </is>
       </c>
       <c r="I67" s="31" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Merge, pull on the server, bench migrate, restart; smoke-test with the Test Cases workbook.</t>
         </is>
       </c>
       <c r="J67" s="31" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="29" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="B68" s="30" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="C68" s="31" t="inlineStr">
         <is>
-          <t>Ministry views for Employees (5) and Students (10)</t>
+          <t>Research: Jameah system, Ministry documents, view contract</t>
         </is>
       </c>
       <c r="D68" s="30" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -5775,29 +5775,29 @@
       </c>
       <c r="G68" s="30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H68" s="31" t="inlineStr">
         <is>
-          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
+          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
         </is>
       </c>
       <c r="I68" s="31" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="J68" s="31" t="inlineStr">
         <is>
-          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
+          <t>Jameah report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="B69" s="30" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C69" s="31" t="inlineStr">
         <is>
-          <t>Code crosswalk (Jameah Code Map)</t>
+          <t>Ministry views for Employees (5) and Students (10)</t>
         </is>
       </c>
       <c r="D69" s="30" t="inlineStr">
@@ -5827,29 +5827,29 @@
       </c>
       <c r="G69" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H69" s="31" t="inlineStr">
         <is>
-          <t>299 college values mapped to official codes by meaning; wrong codes in Education masters (City 90, REL001...) no longer reach the Ministry.</t>
+          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
         </is>
       </c>
       <c r="I69" s="31" t="inlineStr">
         <is>
-          <t>Review 3 values (JM-11).</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="J69" s="31" t="inlineStr">
         <is>
-          <t>jameah/code_map.py</t>
+          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>JM-04</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="B70" s="30" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C70" s="31" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>Code crosswalk (Jameah Code Map)</t>
         </is>
       </c>
       <c r="D70" s="30" t="inlineStr">
@@ -5884,24 +5884,24 @@
       </c>
       <c r="H70" s="31" t="inlineStr">
         <is>
-          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
+          <t>299 college values mapped to official codes by meaning; wrong codes in Education masters (City 90, REL001...) no longer reach the Ministry.</t>
         </is>
       </c>
       <c r="I70" s="31" t="inlineStr">
         <is>
-          <t>Fill 6 values (JM-10).</t>
+          <t>Review 3 values (JM-11).</t>
         </is>
       </c>
       <c r="J70" s="31" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>jameah/code_map.py</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="29" t="inlineStr">
         <is>
-          <t>JM-05</t>
+          <t>JM-04</t>
         </is>
       </c>
       <c r="B71" s="30" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
-          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="D71" s="30" t="inlineStr">
@@ -5936,24 +5936,24 @@
       </c>
       <c r="H71" s="31" t="inlineStr">
         <is>
-          <t>Follows the transcript; view answers in ~3 s instead of 30 s.</t>
+          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Fill 6 values (JM-10).</t>
         </is>
       </c>
       <c r="J71" s="31" t="inlineStr">
         <is>
-          <t>jameah/summary.py</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="29" t="inlineStr">
         <is>
-          <t>JM-06</t>
+          <t>JM-05</t>
         </is>
       </c>
       <c r="B72" s="30" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="C72" s="31" t="inlineStr">
         <is>
-          <t>Independent verification of every view</t>
+          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
         </is>
       </c>
       <c r="D72" s="30" t="inlineStr">
@@ -5983,29 +5983,29 @@
       </c>
       <c r="G72" s="30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H72" s="31" t="inlineStr">
         <is>
-          <t>All 15 views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the Education update (JM-18): all 15 OK.</t>
+          <t>Follows the transcript; view answers in ~3 s instead of 30 s.</t>
         </is>
       </c>
       <c r="I72" s="31" t="inlineStr">
         <is>
-          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="J72" s="31" t="inlineStr">
         <is>
-          <t>jameah/verify.py; test_jameah.py</t>
+          <t>jameah/summary.py</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="29" t="inlineStr">
         <is>
-          <t>JM-18</t>
+          <t>JM-06</t>
         </is>
       </c>
       <c r="B73" s="30" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="C73" s="31" t="inlineStr">
         <is>
-          <t>Ministry GPA and credit hours = the college's official figures</t>
+          <t>Independent verification of every view</t>
         </is>
       </c>
       <c r="D73" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E73" s="30" t="inlineStr">
@@ -6040,24 +6040,24 @@
       </c>
       <c r="H73" s="31" t="inlineStr">
         <is>
-          <t>Found 21 Oct: Education's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads Education's official functions (read only, no change to Education); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
+          <t>All 15 views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the Education update (JM-18): all 15 OK.</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr">
         <is>
-          <t>Deploy together with the Education master update (HR-58); re-run verify on the live server.</t>
+          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="J73" s="31" t="inlineStr">
         <is>
-          <t>jameah/summary.py; jameah/verify.py</t>
+          <t>jameah/verify.py; test_jameah.py</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="29" t="inlineStr">
         <is>
-          <t>JM-07</t>
+          <t>JM-18</t>
         </is>
       </c>
       <c r="B74" s="30" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="C74" s="31" t="inlineStr">
         <is>
-          <t>Jameah Data Check page and Employee preview</t>
+          <t>Ministry GPA and credit hours = the college's official figures</t>
         </is>
       </c>
       <c r="D74" s="30" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
@@ -6087,29 +6087,29 @@
       </c>
       <c r="G74" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H74" s="31" t="inlineStr">
         <is>
-          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
+          <t>Found 21 Oct: Education's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads Education's official functions (read only, no change to Education); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
         </is>
       </c>
       <c r="I74" s="31" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Deploy together with the Education master update (HR-58); re-run verify on the live server.</t>
         </is>
       </c>
       <c r="J74" s="31" t="inlineStr">
         <is>
-          <t>page/jameah_data_check</t>
+          <t>jameah/summary.py; jameah/verify.py</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="29" t="inlineStr">
         <is>
-          <t>JM-08</t>
+          <t>JM-07</t>
         </is>
       </c>
       <c r="B75" s="30" t="inlineStr">
@@ -6119,22 +6119,22 @@
       </c>
       <c r="C75" s="31" t="inlineStr">
         <is>
-          <t>Read-only database account for the Ministry agent</t>
+          <t>Jameah Data Check page and Employee preview</t>
         </is>
       </c>
       <c r="D75" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E75" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F75" s="30" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G75" s="30" t="inlineStr">
@@ -6144,24 +6144,24 @@
       </c>
       <c r="H75" s="31" t="inlineStr">
         <is>
-          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
+          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
         </is>
       </c>
       <c r="I75" s="31" t="inlineStr">
         <is>
-          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="J75" s="31" t="inlineStr">
         <is>
-          <t>jameah/README.md</t>
+          <t>page/jameah_data_check</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="29" t="inlineStr">
         <is>
-          <t>JM-09</t>
+          <t>JM-08</t>
         </is>
       </c>
       <c r="B76" s="30" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="C76" s="31" t="inlineStr">
         <is>
-          <t>Confirm view and column names with the Ministry</t>
+          <t>Read-only database account for the Ministry agent</t>
         </is>
       </c>
       <c r="D76" s="30" t="inlineStr">
@@ -6181,39 +6181,39 @@
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H76" s="31" t="inlineStr">
         <is>
-          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
+          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
         </is>
       </c>
       <c r="I76" s="31" t="inlineStr">
         <is>
-          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
+          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
         </is>
       </c>
       <c r="J76" s="31" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>jameah/README.md</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="29" t="inlineStr">
         <is>
-          <t>JM-10</t>
+          <t>JM-09</t>
         </is>
       </c>
       <c r="B77" s="30" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>Fill Jameah Settings (6 values)</t>
+          <t>Confirm view and column names with the Ministry</t>
         </is>
       </c>
       <c r="D77" s="30" t="inlineStr">
@@ -6238,34 +6238,34 @@
       </c>
       <c r="F77" s="30" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="G77" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H77" s="31" t="inlineStr">
         <is>
-          <t>Empty values are sent as empty.</t>
+          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
         </is>
       </c>
       <c r="I77" s="31" t="inlineStr">
         <is>
-          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
+          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
         </is>
       </c>
       <c r="J77" s="31" t="inlineStr">
         <is>
-          <t>/app/jameah-settings</t>
+          <t>Jameah report</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="29" t="inlineStr">
         <is>
-          <t>JM-11</t>
+          <t>JM-10</t>
         </is>
       </c>
       <c r="B78" s="30" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="C78" s="31" t="inlineStr">
         <is>
-          <t>Map 3 college values to Ministry codes</t>
+          <t>Fill Jameah Settings (6 values)</t>
         </is>
       </c>
       <c r="D78" s="30" t="inlineStr">
@@ -6300,24 +6300,24 @@
       </c>
       <c r="H78" s="31" t="inlineStr">
         <is>
-          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
+          <t>Empty values are sent as empty.</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr">
         <is>
-          <t>Pick the code in Jameah Code Map and set Verified.</t>
+          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
         </is>
       </c>
       <c r="J78" s="31" t="inlineStr">
         <is>
-          <t>/app/jameah-code-map</t>
+          <t>/app/jameah-settings</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="29" t="inlineStr">
         <is>
-          <t>JM-12</t>
+          <t>JM-11</t>
         </is>
       </c>
       <c r="B79" s="30" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="C79" s="31" t="inlineStr">
         <is>
-          <t>Ministry fields with no source in the college system</t>
+          <t>Map 3 college values to Ministry codes</t>
         </is>
       </c>
       <c r="D79" s="30" t="inlineStr">
@@ -6342,34 +6342,34 @@
       </c>
       <c r="F79" s="30" t="inlineStr">
         <is>
-          <t>Academic Affairs + Education team</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="G79" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H79" s="31" t="inlineStr">
         <is>
-          <t>Scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty.</t>
+          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr">
         <is>
-          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
+          <t>Pick the code in Jameah Code Map and set Verified.</t>
         </is>
       </c>
       <c r="J79" s="31" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>/app/jameah-code-map</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="29" t="inlineStr">
         <is>
-          <t>JM-13</t>
+          <t>JM-12</t>
         </is>
       </c>
       <c r="B80" s="30" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="C80" s="31" t="inlineStr">
         <is>
-          <t>Correct source data found by the checks</t>
+          <t>Ministry fields with no source in the college system</t>
         </is>
       </c>
       <c r="D80" s="30" t="inlineStr">
@@ -6389,39 +6389,39 @@
       </c>
       <c r="E80" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Registrar / Education team</t>
+          <t>Academic Affairs + Education team</t>
         </is>
       </c>
       <c r="G80" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H80" s="31" t="inlineStr">
         <is>
-          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
+          <t>Scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty.</t>
         </is>
       </c>
       <c r="I80" s="31" t="inlineStr">
         <is>
-          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
+          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
         </is>
       </c>
       <c r="J80" s="31" t="inlineStr">
         <is>
-          <t>/app/jameah-data-check</t>
+          <t>Jameah report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="29" t="inlineStr">
         <is>
-          <t>JM-14</t>
+          <t>JM-13</t>
         </is>
       </c>
       <c r="B81" s="30" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
-          <t>Faculty views (8 sections)</t>
+          <t>Correct source data found by the checks</t>
         </is>
       </c>
       <c r="D81" s="30" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E81" s="30" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F81" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Registrar / Education team</t>
         </is>
       </c>
       <c r="G81" s="30" t="inlineStr">
@@ -6456,24 +6456,24 @@
       </c>
       <c r="H81" s="31" t="inlineStr">
         <is>
-          <t>Not started (this round covered Employees and Students).</t>
+          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
         </is>
       </c>
       <c r="I81" s="31" t="inlineStr">
         <is>
-          <t>Build and verify the same way.</t>
+          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
         </is>
       </c>
       <c r="J81" s="31" t="inlineStr">
         <is>
-          <t>MINISTRY_FIELD_MAPPING.html</t>
+          <t>/app/jameah-data-check</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
         <is>
-          <t>JM-15</t>
+          <t>JM-14</t>
         </is>
       </c>
       <c r="B82" s="30" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C82" s="31" t="inlineStr">
         <is>
-          <t>Institute views (20 sections)</t>
+          <t>Faculty views (8 sections)</t>
         </is>
       </c>
       <c r="D82" s="30" t="inlineStr">
@@ -6503,17 +6503,17 @@
       </c>
       <c r="G82" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H82" s="31" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Not started (this round covered Employees and Students).</t>
         </is>
       </c>
       <c r="I82" s="31" t="inlineStr">
         <is>
-          <t>Build after Faculty; needs institute data from HR.</t>
+          <t>Build and verify the same way.</t>
         </is>
       </c>
       <c r="J82" s="31" t="inlineStr">
@@ -6525,7 +6525,7 @@
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
         <is>
-          <t>JM-16</t>
+          <t>JM-15</t>
         </is>
       </c>
       <c r="B83" s="30" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="C83" s="31" t="inlineStr">
         <is>
-          <t>Old Education viewJameah* views (42)</t>
+          <t>Institute views (20 sections)</t>
         </is>
       </c>
       <c r="D83" s="30" t="inlineStr">
@@ -6545,90 +6545,142 @@
       </c>
       <c r="E83" s="30" t="inlineStr">
         <is>
-          <t>Pending – other team</t>
+          <t>Pending – development</t>
         </is>
       </c>
       <c r="F83" s="30" t="inlineStr">
         <is>
-          <t>Education team</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G83" s="30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H83" s="31" t="inlineStr">
         <is>
-          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="I83" s="31" t="inlineStr">
         <is>
-          <t>Education team to retire them once ours are confirmed.</t>
+          <t>Build after Faculty; needs institute data from HR.</t>
         </is>
       </c>
       <c r="J83" s="31" t="inlineStr">
         <is>
-          <t>education/jameah_system</t>
+          <t>MINISTRY_FIELD_MAPPING.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
         <is>
+          <t>JM-16</t>
+        </is>
+      </c>
+      <c r="B84" s="30" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C84" s="31" t="inlineStr">
+        <is>
+          <t>Old Education viewJameah* views (42)</t>
+        </is>
+      </c>
+      <c r="D84" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="30" t="inlineStr">
+        <is>
+          <t>Pending – other team</t>
+        </is>
+      </c>
+      <c r="F84" s="30" t="inlineStr">
+        <is>
+          <t>Education team</t>
+        </is>
+      </c>
+      <c r="G84" s="30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H84" s="31" t="inlineStr">
+        <is>
+          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+        </is>
+      </c>
+      <c r="I84" s="31" t="inlineStr">
+        <is>
+          <t>Education team to retire them once ours are confirmed.</t>
+        </is>
+      </c>
+      <c r="J84" s="31" t="inlineStr">
+        <is>
+          <t>education/jameah_system</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="29" t="inlineStr">
+        <is>
           <t>JM-17</t>
         </is>
       </c>
-      <c r="B84" s="30" t="inlineStr">
+      <c r="B85" s="30" t="inlineStr">
         <is>
           <t>Jameah</t>
         </is>
       </c>
-      <c r="C84" s="31" t="inlineStr">
+      <c r="C85" s="31" t="inlineStr">
         <is>
           <t>Transcript GPA rounding at exact ties</t>
         </is>
       </c>
-      <c r="D84" s="30" t="inlineStr">
+      <c r="D85" s="30" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
       </c>
-      <c r="E84" s="30" t="inlineStr">
+      <c r="E85" s="30" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F84" s="30" t="inlineStr">
+      <c r="F85" s="30" t="inlineStr">
         <is>
           <t>Education team</t>
         </is>
       </c>
-      <c r="G84" s="30" t="inlineStr">
+      <c r="G85" s="30" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H84" s="31" t="inlineStr">
+      <c r="H85" s="31" t="inlineStr">
         <is>
           <t>Resolved by Education's new GPA module (exact half-up rounding); the views now use it (JM-18).</t>
         </is>
       </c>
-      <c r="I84" s="31" t="inlineStr">
+      <c r="I85" s="31" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J84" s="31" t="inlineStr">
+      <c r="J85" s="31" t="inlineStr">
         <is>
           <t>Jameah report</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J84"/>
-  <conditionalFormatting sqref="A2:J284">
+  <autoFilter ref="A1:J85"/>
+  <conditionalFormatting sqref="A2:J285">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E2="Done"</formula>
     </cfRule>
@@ -6655,10 +6707,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E284" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
+    <dataValidation sqref="E2:E285" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
       <formula1>"Done,Done – client UAT pending,In progress,Pending – decision needed,Pending – data / setup,Pending – development,Pending – other team,Planned"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G284" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G285" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
